--- a/dataCaseStudy_Cement/raw_results/tech_selection/Summary.xlsx
+++ b/dataCaseStudy_Cement/raw_results/tech_selection/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE329"/>
+  <dimension ref="A1:AE354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34366,6 +34366,2581 @@
       <c r="AE329" t="inlineStr">
         <is>
           <t>dataCaseStudy_Cement\raw_results\tech_selection\20260806125316_carbon_tax_300_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>55807148.464256</v>
+      </c>
+      <c r="B330" t="n">
+        <v>14404244.23429233</v>
+      </c>
+      <c r="C330" t="n">
+        <v>5951746.544758592</v>
+      </c>
+      <c r="D330" t="n">
+        <v>13104127.45045842</v>
+      </c>
+      <c r="E330" t="n">
+        <v>0</v>
+      </c>
+      <c r="F330" t="n">
+        <v>27508371.68475074</v>
+      </c>
+      <c r="G330" t="n">
+        <v>5951746.544758592</v>
+      </c>
+      <c r="H330" t="n">
+        <v>16272107.18482895</v>
+      </c>
+      <c r="I330" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" t="n">
+        <v>0</v>
+      </c>
+      <c r="K330" t="n">
+        <v>0</v>
+      </c>
+      <c r="L330" t="n">
+        <v>6074923.049917719</v>
+      </c>
+      <c r="M330" t="n">
+        <v>55807148.464256</v>
+      </c>
+      <c r="N330" t="n">
+        <v>60756.06478760712</v>
+      </c>
+      <c r="O330" t="n">
+        <v>0</v>
+      </c>
+      <c r="P330" t="n">
+        <v>60756.06478760712</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>60749.23049917654</v>
+      </c>
+      <c r="R330" t="n">
+        <v>0</v>
+      </c>
+      <c r="S330" t="n">
+        <v>0</v>
+      </c>
+      <c r="T330" t="n">
+        <v>0</v>
+      </c>
+      <c r="U330" t="n">
+        <v>6.834288431157361</v>
+      </c>
+      <c r="V330" t="n">
+        <v>32.97300004959106</v>
+      </c>
+      <c r="W330" t="n">
+        <v>55807148.464256</v>
+      </c>
+      <c r="X330" t="n">
+        <v>55807148.464256</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB330" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD330" t="inlineStr">
+        <is>
+          <t>carbon_tax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE330" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007135716_carbon_tax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="B331" t="n">
+        <v>0</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" t="n">
+        <v>0</v>
+      </c>
+      <c r="F331" t="n">
+        <v>0</v>
+      </c>
+      <c r="G331" t="n">
+        <v>0</v>
+      </c>
+      <c r="H331" t="n">
+        <v>0</v>
+      </c>
+      <c r="I331" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" t="n">
+        <v>0</v>
+      </c>
+      <c r="K331" t="n">
+        <v>0</v>
+      </c>
+      <c r="L331" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="M331" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="N331" t="n">
+        <v>607492.3049917679</v>
+      </c>
+      <c r="O331" t="n">
+        <v>0</v>
+      </c>
+      <c r="P331" t="n">
+        <v>607492.3049917679</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>607492.3049917654</v>
+      </c>
+      <c r="R331" t="n">
+        <v>0</v>
+      </c>
+      <c r="S331" t="n">
+        <v>0</v>
+      </c>
+      <c r="T331" t="n">
+        <v>0</v>
+      </c>
+      <c r="U331" t="n">
+        <v>0</v>
+      </c>
+      <c r="V331" t="n">
+        <v>27.98300004005432</v>
+      </c>
+      <c r="W331" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="X331" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB331" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC331" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD331" t="inlineStr">
+        <is>
+          <t>carbon_tax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007140125_carbon_tax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="B332" t="n">
+        <v>0</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" t="n">
+        <v>0</v>
+      </c>
+      <c r="F332" t="n">
+        <v>0</v>
+      </c>
+      <c r="G332" t="n">
+        <v>0</v>
+      </c>
+      <c r="H332" t="n">
+        <v>0</v>
+      </c>
+      <c r="I332" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" t="n">
+        <v>0</v>
+      </c>
+      <c r="K332" t="n">
+        <v>0</v>
+      </c>
+      <c r="L332" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="M332" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="N332" t="n">
+        <v>607492.3049917679</v>
+      </c>
+      <c r="O332" t="n">
+        <v>0</v>
+      </c>
+      <c r="P332" t="n">
+        <v>607492.3049917679</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>607492.3049917654</v>
+      </c>
+      <c r="R332" t="n">
+        <v>0</v>
+      </c>
+      <c r="S332" t="n">
+        <v>0</v>
+      </c>
+      <c r="T332" t="n">
+        <v>0</v>
+      </c>
+      <c r="U332" t="n">
+        <v>0</v>
+      </c>
+      <c r="V332" t="n">
+        <v>27.22500014305115</v>
+      </c>
+      <c r="W332" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="X332" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB332" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD332" t="inlineStr">
+        <is>
+          <t>carbon_tax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE332" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007140516_carbon_tax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="B333" t="n">
+        <v>0</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" t="n">
+        <v>0</v>
+      </c>
+      <c r="F333" t="n">
+        <v>0</v>
+      </c>
+      <c r="G333" t="n">
+        <v>0</v>
+      </c>
+      <c r="H333" t="n">
+        <v>0</v>
+      </c>
+      <c r="I333" t="n">
+        <v>0</v>
+      </c>
+      <c r="J333" t="n">
+        <v>0</v>
+      </c>
+      <c r="K333" t="n">
+        <v>0</v>
+      </c>
+      <c r="L333" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="M333" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="N333" t="n">
+        <v>607492.3049917679</v>
+      </c>
+      <c r="O333" t="n">
+        <v>0</v>
+      </c>
+      <c r="P333" t="n">
+        <v>607492.3049917679</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>607492.3049917654</v>
+      </c>
+      <c r="R333" t="n">
+        <v>0</v>
+      </c>
+      <c r="S333" t="n">
+        <v>0</v>
+      </c>
+      <c r="T333" t="n">
+        <v>0</v>
+      </c>
+      <c r="U333" t="n">
+        <v>0</v>
+      </c>
+      <c r="V333" t="n">
+        <v>21.81599998474121</v>
+      </c>
+      <c r="W333" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="X333" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB333" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC333" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD333" t="inlineStr">
+        <is>
+          <t>carbon_tax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE333" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007140932_carbon_tax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="B334" t="n">
+        <v>0</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>0</v>
+      </c>
+      <c r="F334" t="n">
+        <v>0</v>
+      </c>
+      <c r="G334" t="n">
+        <v>0</v>
+      </c>
+      <c r="H334" t="n">
+        <v>0</v>
+      </c>
+      <c r="I334" t="n">
+        <v>0</v>
+      </c>
+      <c r="J334" t="n">
+        <v>0</v>
+      </c>
+      <c r="K334" t="n">
+        <v>0</v>
+      </c>
+      <c r="L334" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="M334" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="N334" t="n">
+        <v>607492.3049917679</v>
+      </c>
+      <c r="O334" t="n">
+        <v>0</v>
+      </c>
+      <c r="P334" t="n">
+        <v>607492.3049917679</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>607492.3049917654</v>
+      </c>
+      <c r="R334" t="n">
+        <v>0</v>
+      </c>
+      <c r="S334" t="n">
+        <v>0</v>
+      </c>
+      <c r="T334" t="n">
+        <v>0</v>
+      </c>
+      <c r="U334" t="n">
+        <v>0</v>
+      </c>
+      <c r="V334" t="n">
+        <v>22.28400015830994</v>
+      </c>
+      <c r="W334" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="X334" t="n">
+        <v>60749230.49917586</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD334" t="inlineStr">
+        <is>
+          <t>carbon_tax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE334" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007141312_carbon_tax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>58844609.98921474</v>
+      </c>
+      <c r="B335" t="n">
+        <v>14404244.23429233</v>
+      </c>
+      <c r="C335" t="n">
+        <v>5951746.544758592</v>
+      </c>
+      <c r="D335" t="n">
+        <v>13104127.45045846</v>
+      </c>
+      <c r="E335" t="n">
+        <v>0</v>
+      </c>
+      <c r="F335" t="n">
+        <v>27508371.68475079</v>
+      </c>
+      <c r="G335" t="n">
+        <v>5951746.544758592</v>
+      </c>
+      <c r="H335" t="n">
+        <v>16272107.18482895</v>
+      </c>
+      <c r="I335" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" t="n">
+        <v>0</v>
+      </c>
+      <c r="K335" t="n">
+        <v>0</v>
+      </c>
+      <c r="L335" t="n">
+        <v>9112384.574876415</v>
+      </c>
+      <c r="M335" t="n">
+        <v>58844609.98921474</v>
+      </c>
+      <c r="N335" t="n">
+        <v>60756.06478760713</v>
+      </c>
+      <c r="O335" t="n">
+        <v>0</v>
+      </c>
+      <c r="P335" t="n">
+        <v>60756.06478760713</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>60749.23049917648</v>
+      </c>
+      <c r="R335" t="n">
+        <v>0</v>
+      </c>
+      <c r="S335" t="n">
+        <v>0</v>
+      </c>
+      <c r="T335" t="n">
+        <v>0</v>
+      </c>
+      <c r="U335" t="n">
+        <v>6.834288431157361</v>
+      </c>
+      <c r="V335" t="n">
+        <v>24.18499994277954</v>
+      </c>
+      <c r="W335" t="n">
+        <v>58844609.98920792</v>
+      </c>
+      <c r="X335" t="n">
+        <v>58844609.98921474</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>6.824731826782227e-06</v>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD335" t="inlineStr">
+        <is>
+          <t>carbon_tax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE335" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007141714_carbon_tax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>66153055.21150209</v>
+      </c>
+      <c r="B336" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C336" t="n">
+        <v>6725637.346347707</v>
+      </c>
+      <c r="D336" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E336" t="n">
+        <v>0</v>
+      </c>
+      <c r="F336" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G336" t="n">
+        <v>6725637.346347707</v>
+      </c>
+      <c r="H336" t="n">
+        <v>14183168.38067319</v>
+      </c>
+      <c r="I336" t="n">
+        <v>0</v>
+      </c>
+      <c r="J336" t="n">
+        <v>0</v>
+      </c>
+      <c r="K336" t="n">
+        <v>0</v>
+      </c>
+      <c r="L336" t="n">
+        <v>1085645.259932351</v>
+      </c>
+      <c r="M336" t="n">
+        <v>66153055.21150209</v>
+      </c>
+      <c r="N336" t="n">
+        <v>7245.844635991053</v>
+      </c>
+      <c r="O336" t="n">
+        <v>0</v>
+      </c>
+      <c r="P336" t="n">
+        <v>7245.844635991053</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>7237.635066215645</v>
+      </c>
+      <c r="R336" t="n">
+        <v>0</v>
+      </c>
+      <c r="S336" t="n">
+        <v>0</v>
+      </c>
+      <c r="T336" t="n">
+        <v>0</v>
+      </c>
+      <c r="U336" t="n">
+        <v>8.209569775222587</v>
+      </c>
+      <c r="V336" t="n">
+        <v>20.4060001373291</v>
+      </c>
+      <c r="W336" t="n">
+        <v>66153055.2114955</v>
+      </c>
+      <c r="X336" t="n">
+        <v>66153055.21150209</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>6.586313247680664e-06</v>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB336" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC336" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD336" t="inlineStr">
+        <is>
+          <t>carbon_tax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE336" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007142125_carbon_tax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>72026443.23962373</v>
+      </c>
+      <c r="B337" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C337" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="D337" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
+      <c r="F337" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G337" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="H337" t="n">
+        <v>20056556.40879477</v>
+      </c>
+      <c r="I337" t="n">
+        <v>0</v>
+      </c>
+      <c r="J337" t="n">
+        <v>0</v>
+      </c>
+      <c r="K337" t="n">
+        <v>0</v>
+      </c>
+      <c r="L337" t="n">
+        <v>1085645.259932396</v>
+      </c>
+      <c r="M337" t="n">
+        <v>72026443.23962373</v>
+      </c>
+      <c r="N337" t="n">
+        <v>7245.844635991023</v>
+      </c>
+      <c r="O337" t="n">
+        <v>0</v>
+      </c>
+      <c r="P337" t="n">
+        <v>7245.844635991023</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>7237.635066215884</v>
+      </c>
+      <c r="R337" t="n">
+        <v>0</v>
+      </c>
+      <c r="S337" t="n">
+        <v>0</v>
+      </c>
+      <c r="T337" t="n">
+        <v>0</v>
+      </c>
+      <c r="U337" t="n">
+        <v>8.209569775222583</v>
+      </c>
+      <c r="V337" t="n">
+        <v>19.72900009155273</v>
+      </c>
+      <c r="W337" t="n">
+        <v>72026443.23961693</v>
+      </c>
+      <c r="X337" t="n">
+        <v>72026443.23962373</v>
+      </c>
+      <c r="Y337" t="n">
+        <v>6.794929504394531e-06</v>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB337" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC337" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD337" t="inlineStr">
+        <is>
+          <t>carbon_tax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE337" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007142545_carbon_tax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>76318472.79089154</v>
+      </c>
+      <c r="B338" t="n">
+        <v>13228586.17399643</v>
+      </c>
+      <c r="C338" t="n">
+        <v>5758365.764824538</v>
+      </c>
+      <c r="D338" t="n">
+        <v>23703694.55346578</v>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+      <c r="F338" t="n">
+        <v>36932280.72746221</v>
+      </c>
+      <c r="G338" t="n">
+        <v>5758365.764824538</v>
+      </c>
+      <c r="H338" t="n">
+        <v>11914921.09995709</v>
+      </c>
+      <c r="I338" t="n">
+        <v>0</v>
+      </c>
+      <c r="J338" t="n">
+        <v>0</v>
+      </c>
+      <c r="K338" t="n">
+        <v>0</v>
+      </c>
+      <c r="L338" t="n">
+        <v>21712905.1986477</v>
+      </c>
+      <c r="M338" t="n">
+        <v>76318472.79089154</v>
+      </c>
+      <c r="N338" t="n">
+        <v>144759.1919557629</v>
+      </c>
+      <c r="O338" t="n">
+        <v>0</v>
+      </c>
+      <c r="P338" t="n">
+        <v>144759.1919557629</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>144752.701324317</v>
+      </c>
+      <c r="R338" t="n">
+        <v>0</v>
+      </c>
+      <c r="S338" t="n">
+        <v>0</v>
+      </c>
+      <c r="T338" t="n">
+        <v>0</v>
+      </c>
+      <c r="U338" t="n">
+        <v>6.49063144699632</v>
+      </c>
+      <c r="V338" t="n">
+        <v>17.76199984550476</v>
+      </c>
+      <c r="W338" t="n">
+        <v>76318472.79088475</v>
+      </c>
+      <c r="X338" t="n">
+        <v>76318472.79089154</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>6.794929504394531e-06</v>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB338" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC338" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD338" t="inlineStr">
+        <is>
+          <t>carbon_tax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE338" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007142840_carbon_tax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>78688104.98477326</v>
+      </c>
+      <c r="B339" t="n">
+        <v>13228586.17399643</v>
+      </c>
+      <c r="C339" t="n">
+        <v>5758365.764824538</v>
+      </c>
+      <c r="D339" t="n">
+        <v>23703694.55346578</v>
+      </c>
+      <c r="E339" t="n">
+        <v>0</v>
+      </c>
+      <c r="F339" t="n">
+        <v>36932280.72746221</v>
+      </c>
+      <c r="G339" t="n">
+        <v>5758365.764824538</v>
+      </c>
+      <c r="H339" t="n">
+        <v>14284553.29383882</v>
+      </c>
+      <c r="I339" t="n">
+        <v>0</v>
+      </c>
+      <c r="J339" t="n">
+        <v>0</v>
+      </c>
+      <c r="K339" t="n">
+        <v>0</v>
+      </c>
+      <c r="L339" t="n">
+        <v>21712905.1986477</v>
+      </c>
+      <c r="M339" t="n">
+        <v>78688104.98477326</v>
+      </c>
+      <c r="N339" t="n">
+        <v>144759.1919557629</v>
+      </c>
+      <c r="O339" t="n">
+        <v>0</v>
+      </c>
+      <c r="P339" t="n">
+        <v>144759.1919557629</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>144752.701324317</v>
+      </c>
+      <c r="R339" t="n">
+        <v>0</v>
+      </c>
+      <c r="S339" t="n">
+        <v>0</v>
+      </c>
+      <c r="T339" t="n">
+        <v>0</v>
+      </c>
+      <c r="U339" t="n">
+        <v>6.49063144699632</v>
+      </c>
+      <c r="V339" t="n">
+        <v>16.86300015449524</v>
+      </c>
+      <c r="W339" t="n">
+        <v>78688104.98476642</v>
+      </c>
+      <c r="X339" t="n">
+        <v>78688104.98477326</v>
+      </c>
+      <c r="Y339" t="n">
+        <v>6.839632987976074e-06</v>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB339" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC339" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD339" t="inlineStr">
+        <is>
+          <t>carbon_tax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE339" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007143317_carbon_tax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>60641548.93669145</v>
+      </c>
+      <c r="B340" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C340" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="D340" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E340" t="n">
+        <v>0</v>
+      </c>
+      <c r="F340" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G340" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="H340" t="n">
+        <v>8309780.352551687</v>
+      </c>
+      <c r="I340" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" t="n">
+        <v>0</v>
+      </c>
+      <c r="K340" t="n">
+        <v>0</v>
+      </c>
+      <c r="L340" t="n">
+        <v>1447527.013243214</v>
+      </c>
+      <c r="M340" t="n">
+        <v>60641548.93669145</v>
+      </c>
+      <c r="N340" t="n">
+        <v>7245.844635991112</v>
+      </c>
+      <c r="O340" t="n">
+        <v>0</v>
+      </c>
+      <c r="P340" t="n">
+        <v>7245.844635991112</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>7237.635066215948</v>
+      </c>
+      <c r="R340" t="n">
+        <v>0</v>
+      </c>
+      <c r="S340" t="n">
+        <v>0</v>
+      </c>
+      <c r="T340" t="n">
+        <v>0</v>
+      </c>
+      <c r="U340" t="n">
+        <v>8.209569775222583</v>
+      </c>
+      <c r="V340" t="n">
+        <v>22.65299987792969</v>
+      </c>
+      <c r="W340" t="n">
+        <v>60641548.93669145</v>
+      </c>
+      <c r="X340" t="n">
+        <v>60641548.93669145</v>
+      </c>
+      <c r="Y340" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB340" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC340" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD340" t="inlineStr">
+        <is>
+          <t>carbon_tax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE340" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007143610_carbon_tax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>66514936.96481296</v>
+      </c>
+      <c r="B341" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C341" t="n">
+        <v>6725637.346347707</v>
+      </c>
+      <c r="D341" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
+      <c r="F341" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G341" t="n">
+        <v>6725637.346347707</v>
+      </c>
+      <c r="H341" t="n">
+        <v>14183168.38067319</v>
+      </c>
+      <c r="I341" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" t="n">
+        <v>0</v>
+      </c>
+      <c r="K341" t="n">
+        <v>0</v>
+      </c>
+      <c r="L341" t="n">
+        <v>1447527.013243225</v>
+      </c>
+      <c r="M341" t="n">
+        <v>66514936.96481296</v>
+      </c>
+      <c r="N341" t="n">
+        <v>7245.844635991161</v>
+      </c>
+      <c r="O341" t="n">
+        <v>0</v>
+      </c>
+      <c r="P341" t="n">
+        <v>7245.844635991161</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>7237.635066215978</v>
+      </c>
+      <c r="R341" t="n">
+        <v>0</v>
+      </c>
+      <c r="S341" t="n">
+        <v>0</v>
+      </c>
+      <c r="T341" t="n">
+        <v>0</v>
+      </c>
+      <c r="U341" t="n">
+        <v>8.209569775222583</v>
+      </c>
+      <c r="V341" t="n">
+        <v>18.38499999046326</v>
+      </c>
+      <c r="W341" t="n">
+        <v>66514936.96481296</v>
+      </c>
+      <c r="X341" t="n">
+        <v>66514936.96481296</v>
+      </c>
+      <c r="Y341" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB341" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC341" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD341" t="inlineStr">
+        <is>
+          <t>carbon_tax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE341" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007144119_carbon_tax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>72388324.99293448</v>
+      </c>
+      <c r="B342" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C342" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="D342" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0</v>
+      </c>
+      <c r="F342" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G342" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="H342" t="n">
+        <v>20056556.40879478</v>
+      </c>
+      <c r="I342" t="n">
+        <v>0</v>
+      </c>
+      <c r="J342" t="n">
+        <v>0</v>
+      </c>
+      <c r="K342" t="n">
+        <v>0</v>
+      </c>
+      <c r="L342" t="n">
+        <v>1447527.013243151</v>
+      </c>
+      <c r="M342" t="n">
+        <v>72388324.99293448</v>
+      </c>
+      <c r="N342" t="n">
+        <v>7245.844635991019</v>
+      </c>
+      <c r="O342" t="n">
+        <v>0</v>
+      </c>
+      <c r="P342" t="n">
+        <v>7245.844635991019</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>7237.635066215646</v>
+      </c>
+      <c r="R342" t="n">
+        <v>0</v>
+      </c>
+      <c r="S342" t="n">
+        <v>0</v>
+      </c>
+      <c r="T342" t="n">
+        <v>0</v>
+      </c>
+      <c r="U342" t="n">
+        <v>8.209569775222587</v>
+      </c>
+      <c r="V342" t="n">
+        <v>18.91699981689453</v>
+      </c>
+      <c r="W342" t="n">
+        <v>72388324.99293448</v>
+      </c>
+      <c r="X342" t="n">
+        <v>72388324.99293448</v>
+      </c>
+      <c r="Y342" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB342" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC342" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD342" t="inlineStr">
+        <is>
+          <t>carbon_tax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE342" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007144414_carbon_tax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>78261713.02105595</v>
+      </c>
+      <c r="B343" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C343" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="D343" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E343" t="n">
+        <v>0</v>
+      </c>
+      <c r="F343" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G343" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="H343" t="n">
+        <v>25929944.4369162</v>
+      </c>
+      <c r="I343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" t="n">
+        <v>0</v>
+      </c>
+      <c r="K343" t="n">
+        <v>0</v>
+      </c>
+      <c r="L343" t="n">
+        <v>1447527.013243193</v>
+      </c>
+      <c r="M343" t="n">
+        <v>78261713.02105595</v>
+      </c>
+      <c r="N343" t="n">
+        <v>7245.844635991023</v>
+      </c>
+      <c r="O343" t="n">
+        <v>0</v>
+      </c>
+      <c r="P343" t="n">
+        <v>7245.844635991023</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>7237.635066215884</v>
+      </c>
+      <c r="R343" t="n">
+        <v>0</v>
+      </c>
+      <c r="S343" t="n">
+        <v>0</v>
+      </c>
+      <c r="T343" t="n">
+        <v>0</v>
+      </c>
+      <c r="U343" t="n">
+        <v>8.209569775222583</v>
+      </c>
+      <c r="V343" t="n">
+        <v>18.33299994468689</v>
+      </c>
+      <c r="W343" t="n">
+        <v>78261713.02105595</v>
+      </c>
+      <c r="X343" t="n">
+        <v>78261713.02105595</v>
+      </c>
+      <c r="Y343" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB343" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC343" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD343" t="inlineStr">
+        <is>
+          <t>carbon_tax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE343" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007144940_carbon_tax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>84135101.04917747</v>
+      </c>
+      <c r="B344" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C344" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="D344" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E344" t="n">
+        <v>0</v>
+      </c>
+      <c r="F344" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G344" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="H344" t="n">
+        <v>31803332.46503772</v>
+      </c>
+      <c r="I344" t="n">
+        <v>0</v>
+      </c>
+      <c r="J344" t="n">
+        <v>0</v>
+      </c>
+      <c r="K344" t="n">
+        <v>0</v>
+      </c>
+      <c r="L344" t="n">
+        <v>1447527.013243193</v>
+      </c>
+      <c r="M344" t="n">
+        <v>84135101.04917747</v>
+      </c>
+      <c r="N344" t="n">
+        <v>7245.844635991023</v>
+      </c>
+      <c r="O344" t="n">
+        <v>0</v>
+      </c>
+      <c r="P344" t="n">
+        <v>7245.844635991023</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>7237.635066215884</v>
+      </c>
+      <c r="R344" t="n">
+        <v>0</v>
+      </c>
+      <c r="S344" t="n">
+        <v>0</v>
+      </c>
+      <c r="T344" t="n">
+        <v>0</v>
+      </c>
+      <c r="U344" t="n">
+        <v>8.209569775222583</v>
+      </c>
+      <c r="V344" t="n">
+        <v>17.6470000743866</v>
+      </c>
+      <c r="W344" t="n">
+        <v>84135101.04917747</v>
+      </c>
+      <c r="X344" t="n">
+        <v>84135101.04917747</v>
+      </c>
+      <c r="Y344" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB344" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC344" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD344" t="inlineStr">
+        <is>
+          <t>carbon_tax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE344" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007145236_carbon_tax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>61003430.69000221</v>
+      </c>
+      <c r="B345" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C345" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="D345" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E345" t="n">
+        <v>0</v>
+      </c>
+      <c r="F345" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G345" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="H345" t="n">
+        <v>8309780.352551687</v>
+      </c>
+      <c r="I345" t="n">
+        <v>0</v>
+      </c>
+      <c r="J345" t="n">
+        <v>0</v>
+      </c>
+      <c r="K345" t="n">
+        <v>0</v>
+      </c>
+      <c r="L345" t="n">
+        <v>1809408.766553977</v>
+      </c>
+      <c r="M345" t="n">
+        <v>61003430.69000221</v>
+      </c>
+      <c r="N345" t="n">
+        <v>7245.844635991118</v>
+      </c>
+      <c r="O345" t="n">
+        <v>0</v>
+      </c>
+      <c r="P345" t="n">
+        <v>7245.844635991118</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>7237.635066215947</v>
+      </c>
+      <c r="R345" t="n">
+        <v>0</v>
+      </c>
+      <c r="S345" t="n">
+        <v>0</v>
+      </c>
+      <c r="T345" t="n">
+        <v>0</v>
+      </c>
+      <c r="U345" t="n">
+        <v>8.209569775222583</v>
+      </c>
+      <c r="V345" t="n">
+        <v>18.51800012588501</v>
+      </c>
+      <c r="W345" t="n">
+        <v>61003430.69000221</v>
+      </c>
+      <c r="X345" t="n">
+        <v>61003430.69000221</v>
+      </c>
+      <c r="Y345" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB345" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC345" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD345" t="inlineStr">
+        <is>
+          <t>carbon_tax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE345" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007145533_carbon_tax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>66876818.7181237</v>
+      </c>
+      <c r="B346" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C346" t="n">
+        <v>6725637.34634771</v>
+      </c>
+      <c r="D346" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E346" t="n">
+        <v>0</v>
+      </c>
+      <c r="F346" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G346" t="n">
+        <v>6725637.34634771</v>
+      </c>
+      <c r="H346" t="n">
+        <v>14183168.38067319</v>
+      </c>
+      <c r="I346" t="n">
+        <v>0</v>
+      </c>
+      <c r="J346" t="n">
+        <v>0</v>
+      </c>
+      <c r="K346" t="n">
+        <v>0</v>
+      </c>
+      <c r="L346" t="n">
+        <v>1809408.766553956</v>
+      </c>
+      <c r="M346" t="n">
+        <v>66876818.7181237</v>
+      </c>
+      <c r="N346" t="n">
+        <v>7245.844635991072</v>
+      </c>
+      <c r="O346" t="n">
+        <v>0</v>
+      </c>
+      <c r="P346" t="n">
+        <v>7245.844635991072</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>7237.63506621579</v>
+      </c>
+      <c r="R346" t="n">
+        <v>0</v>
+      </c>
+      <c r="S346" t="n">
+        <v>0</v>
+      </c>
+      <c r="T346" t="n">
+        <v>0</v>
+      </c>
+      <c r="U346" t="n">
+        <v>8.209569775222585</v>
+      </c>
+      <c r="V346" t="n">
+        <v>18.28900003433228</v>
+      </c>
+      <c r="W346" t="n">
+        <v>66876818.7181237</v>
+      </c>
+      <c r="X346" t="n">
+        <v>66876818.7181237</v>
+      </c>
+      <c r="Y346" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB346" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC346" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD346" t="inlineStr">
+        <is>
+          <t>carbon_tax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE346" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007150115_carbon_tax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>72750206.74624528</v>
+      </c>
+      <c r="B347" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C347" t="n">
+        <v>6725637.34634771</v>
+      </c>
+      <c r="D347" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E347" t="n">
+        <v>0</v>
+      </c>
+      <c r="F347" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G347" t="n">
+        <v>6725637.34634771</v>
+      </c>
+      <c r="H347" t="n">
+        <v>20056556.40879477</v>
+      </c>
+      <c r="I347" t="n">
+        <v>0</v>
+      </c>
+      <c r="J347" t="n">
+        <v>0</v>
+      </c>
+      <c r="K347" t="n">
+        <v>0</v>
+      </c>
+      <c r="L347" t="n">
+        <v>1809408.766553947</v>
+      </c>
+      <c r="M347" t="n">
+        <v>72750206.74624528</v>
+      </c>
+      <c r="N347" t="n">
+        <v>7245.844635991076</v>
+      </c>
+      <c r="O347" t="n">
+        <v>0</v>
+      </c>
+      <c r="P347" t="n">
+        <v>7245.844635991076</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>7237.635066215727</v>
+      </c>
+      <c r="R347" t="n">
+        <v>0</v>
+      </c>
+      <c r="S347" t="n">
+        <v>0</v>
+      </c>
+      <c r="T347" t="n">
+        <v>0</v>
+      </c>
+      <c r="U347" t="n">
+        <v>8.209569775222587</v>
+      </c>
+      <c r="V347" t="n">
+        <v>21.33200001716614</v>
+      </c>
+      <c r="W347" t="n">
+        <v>72750206.74624528</v>
+      </c>
+      <c r="X347" t="n">
+        <v>72750206.74624528</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC347" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD347" t="inlineStr">
+        <is>
+          <t>carbon_tax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE347" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007150412_carbon_tax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>78623594.77436669</v>
+      </c>
+      <c r="B348" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C348" t="n">
+        <v>6725637.346347707</v>
+      </c>
+      <c r="D348" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
+      <c r="F348" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G348" t="n">
+        <v>6725637.346347707</v>
+      </c>
+      <c r="H348" t="n">
+        <v>25929944.43691621</v>
+      </c>
+      <c r="I348" t="n">
+        <v>0</v>
+      </c>
+      <c r="J348" t="n">
+        <v>0</v>
+      </c>
+      <c r="K348" t="n">
+        <v>0</v>
+      </c>
+      <c r="L348" t="n">
+        <v>1809408.766553936</v>
+      </c>
+      <c r="M348" t="n">
+        <v>78623594.77436669</v>
+      </c>
+      <c r="N348" t="n">
+        <v>7245.844635991043</v>
+      </c>
+      <c r="O348" t="n">
+        <v>0</v>
+      </c>
+      <c r="P348" t="n">
+        <v>7245.844635991043</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>7237.635066215661</v>
+      </c>
+      <c r="R348" t="n">
+        <v>0</v>
+      </c>
+      <c r="S348" t="n">
+        <v>0</v>
+      </c>
+      <c r="T348" t="n">
+        <v>0</v>
+      </c>
+      <c r="U348" t="n">
+        <v>8.209569775222587</v>
+      </c>
+      <c r="V348" t="n">
+        <v>19.59700012207031</v>
+      </c>
+      <c r="W348" t="n">
+        <v>78623594.77436669</v>
+      </c>
+      <c r="X348" t="n">
+        <v>78623594.77436669</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD348" t="inlineStr">
+        <is>
+          <t>carbon_tax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE348" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007150713_carbon_tax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>84496982.80248822</v>
+      </c>
+      <c r="B349" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C349" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="D349" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E349" t="n">
+        <v>0</v>
+      </c>
+      <c r="F349" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G349" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="H349" t="n">
+        <v>31803332.46503772</v>
+      </c>
+      <c r="I349" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" t="n">
+        <v>0</v>
+      </c>
+      <c r="K349" t="n">
+        <v>0</v>
+      </c>
+      <c r="L349" t="n">
+        <v>1809408.766553953</v>
+      </c>
+      <c r="M349" t="n">
+        <v>84496982.80248822</v>
+      </c>
+      <c r="N349" t="n">
+        <v>7245.844635991023</v>
+      </c>
+      <c r="O349" t="n">
+        <v>0</v>
+      </c>
+      <c r="P349" t="n">
+        <v>7245.844635991023</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>7237.635066215884</v>
+      </c>
+      <c r="R349" t="n">
+        <v>0</v>
+      </c>
+      <c r="S349" t="n">
+        <v>0</v>
+      </c>
+      <c r="T349" t="n">
+        <v>0</v>
+      </c>
+      <c r="U349" t="n">
+        <v>8.209569775222583</v>
+      </c>
+      <c r="V349" t="n">
+        <v>22.59400010108948</v>
+      </c>
+      <c r="W349" t="n">
+        <v>84496982.80248822</v>
+      </c>
+      <c r="X349" t="n">
+        <v>84496982.80248822</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB349" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC349" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD349" t="inlineStr">
+        <is>
+          <t>carbon_tax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE349" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007151011_carbon_tax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>61365312.44331304</v>
+      </c>
+      <c r="B350" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C350" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="D350" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E350" t="n">
+        <v>0</v>
+      </c>
+      <c r="F350" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G350" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="H350" t="n">
+        <v>8309780.352551687</v>
+      </c>
+      <c r="I350" t="n">
+        <v>0</v>
+      </c>
+      <c r="J350" t="n">
+        <v>0</v>
+      </c>
+      <c r="K350" t="n">
+        <v>0</v>
+      </c>
+      <c r="L350" t="n">
+        <v>2171290.519864806</v>
+      </c>
+      <c r="M350" t="n">
+        <v>61365312.44331304</v>
+      </c>
+      <c r="N350" t="n">
+        <v>7245.844635991077</v>
+      </c>
+      <c r="O350" t="n">
+        <v>0</v>
+      </c>
+      <c r="P350" t="n">
+        <v>7245.844635991077</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>7237.635066215918</v>
+      </c>
+      <c r="R350" t="n">
+        <v>0</v>
+      </c>
+      <c r="S350" t="n">
+        <v>0</v>
+      </c>
+      <c r="T350" t="n">
+        <v>0</v>
+      </c>
+      <c r="U350" t="n">
+        <v>8.209569775222583</v>
+      </c>
+      <c r="V350" t="n">
+        <v>19.03600001335144</v>
+      </c>
+      <c r="W350" t="n">
+        <v>61365312.44329876</v>
+      </c>
+      <c r="X350" t="n">
+        <v>61365312.44331304</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>1.428276300430298e-05</v>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB350" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD350" t="inlineStr">
+        <is>
+          <t>carbon_tax_300_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE350" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007151648_carbon_tax_300_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>67238700.47143447</v>
+      </c>
+      <c r="B351" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C351" t="n">
+        <v>6725637.34634771</v>
+      </c>
+      <c r="D351" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E351" t="n">
+        <v>0</v>
+      </c>
+      <c r="F351" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G351" t="n">
+        <v>6725637.34634771</v>
+      </c>
+      <c r="H351" t="n">
+        <v>14183168.38067319</v>
+      </c>
+      <c r="I351" t="n">
+        <v>0</v>
+      </c>
+      <c r="J351" t="n">
+        <v>0</v>
+      </c>
+      <c r="K351" t="n">
+        <v>0</v>
+      </c>
+      <c r="L351" t="n">
+        <v>2171290.519864736</v>
+      </c>
+      <c r="M351" t="n">
+        <v>67238700.47143447</v>
+      </c>
+      <c r="N351" t="n">
+        <v>7245.844635990978</v>
+      </c>
+      <c r="O351" t="n">
+        <v>0</v>
+      </c>
+      <c r="P351" t="n">
+        <v>7245.844635990978</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>7237.635066215838</v>
+      </c>
+      <c r="R351" t="n">
+        <v>0</v>
+      </c>
+      <c r="S351" t="n">
+        <v>0</v>
+      </c>
+      <c r="T351" t="n">
+        <v>0</v>
+      </c>
+      <c r="U351" t="n">
+        <v>8.209569775222587</v>
+      </c>
+      <c r="V351" t="n">
+        <v>19.74799990653992</v>
+      </c>
+      <c r="W351" t="n">
+        <v>67238700.47142044</v>
+      </c>
+      <c r="X351" t="n">
+        <v>67238700.47143447</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>1.403689384460449e-05</v>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC351" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD351" t="inlineStr">
+        <is>
+          <t>carbon_tax_300_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE351" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007151948_carbon_tax_300_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>73112088.49955608</v>
+      </c>
+      <c r="B352" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C352" t="n">
+        <v>6725637.346347711</v>
+      </c>
+      <c r="D352" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
+      <c r="F352" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G352" t="n">
+        <v>6725637.346347711</v>
+      </c>
+      <c r="H352" t="n">
+        <v>20056556.40879477</v>
+      </c>
+      <c r="I352" t="n">
+        <v>0</v>
+      </c>
+      <c r="J352" t="n">
+        <v>0</v>
+      </c>
+      <c r="K352" t="n">
+        <v>0</v>
+      </c>
+      <c r="L352" t="n">
+        <v>2171290.519864756</v>
+      </c>
+      <c r="M352" t="n">
+        <v>73112088.49955608</v>
+      </c>
+      <c r="N352" t="n">
+        <v>7245.84463599107</v>
+      </c>
+      <c r="O352" t="n">
+        <v>0</v>
+      </c>
+      <c r="P352" t="n">
+        <v>7245.84463599107</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>7237.635066215774</v>
+      </c>
+      <c r="R352" t="n">
+        <v>0</v>
+      </c>
+      <c r="S352" t="n">
+        <v>0</v>
+      </c>
+      <c r="T352" t="n">
+        <v>0</v>
+      </c>
+      <c r="U352" t="n">
+        <v>8.209569775222585</v>
+      </c>
+      <c r="V352" t="n">
+        <v>20.4520001411438</v>
+      </c>
+      <c r="W352" t="n">
+        <v>73112088.49954224</v>
+      </c>
+      <c r="X352" t="n">
+        <v>73112088.49955608</v>
+      </c>
+      <c r="Y352" t="n">
+        <v>1.384317874908447e-05</v>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB352" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD352" t="inlineStr">
+        <is>
+          <t>carbon_tax_300_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE352" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007152251_carbon_tax_300_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>78985476.52767749</v>
+      </c>
+      <c r="B353" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C353" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="D353" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E353" t="n">
+        <v>0</v>
+      </c>
+      <c r="F353" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G353" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="H353" t="n">
+        <v>25929944.4369162</v>
+      </c>
+      <c r="I353" t="n">
+        <v>0</v>
+      </c>
+      <c r="J353" t="n">
+        <v>0</v>
+      </c>
+      <c r="K353" t="n">
+        <v>0</v>
+      </c>
+      <c r="L353" t="n">
+        <v>2171290.519864731</v>
+      </c>
+      <c r="M353" t="n">
+        <v>78985476.52767749</v>
+      </c>
+      <c r="N353" t="n">
+        <v>7245.844635991041</v>
+      </c>
+      <c r="O353" t="n">
+        <v>0</v>
+      </c>
+      <c r="P353" t="n">
+        <v>7245.844635991041</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>7237.63506621571</v>
+      </c>
+      <c r="R353" t="n">
+        <v>0</v>
+      </c>
+      <c r="S353" t="n">
+        <v>0</v>
+      </c>
+      <c r="T353" t="n">
+        <v>0</v>
+      </c>
+      <c r="U353" t="n">
+        <v>8.209569775222587</v>
+      </c>
+      <c r="V353" t="n">
+        <v>20.63599991798401</v>
+      </c>
+      <c r="W353" t="n">
+        <v>78985476.52766423</v>
+      </c>
+      <c r="X353" t="n">
+        <v>78985476.52767749</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>1.326203346252441e-05</v>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB353" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC353" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD353" t="inlineStr">
+        <is>
+          <t>carbon_tax_300_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE353" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007152553_carbon_tax_300_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>84858864.55579896</v>
+      </c>
+      <c r="B354" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C354" t="n">
+        <v>6725637.346347711</v>
+      </c>
+      <c r="D354" t="n">
+        <v>26513229.33165425</v>
+      </c>
+      <c r="E354" t="n">
+        <v>0</v>
+      </c>
+      <c r="F354" t="n">
+        <v>44158604.22454884</v>
+      </c>
+      <c r="G354" t="n">
+        <v>6725637.346347711</v>
+      </c>
+      <c r="H354" t="n">
+        <v>31803332.46503773</v>
+      </c>
+      <c r="I354" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" t="n">
+        <v>0</v>
+      </c>
+      <c r="K354" t="n">
+        <v>0</v>
+      </c>
+      <c r="L354" t="n">
+        <v>2171290.519864699</v>
+      </c>
+      <c r="M354" t="n">
+        <v>84858864.55579896</v>
+      </c>
+      <c r="N354" t="n">
+        <v>7245.844635991021</v>
+      </c>
+      <c r="O354" t="n">
+        <v>0</v>
+      </c>
+      <c r="P354" t="n">
+        <v>7245.844635991021</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>7237.635066215645</v>
+      </c>
+      <c r="R354" t="n">
+        <v>0</v>
+      </c>
+      <c r="S354" t="n">
+        <v>0</v>
+      </c>
+      <c r="T354" t="n">
+        <v>0</v>
+      </c>
+      <c r="U354" t="n">
+        <v>8.209569775222587</v>
+      </c>
+      <c r="V354" t="n">
+        <v>19.98900008201599</v>
+      </c>
+      <c r="W354" t="n">
+        <v>84858864.55578578</v>
+      </c>
+      <c r="X354" t="n">
+        <v>84858864.55579896</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>1.318752765655518e-05</v>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB354" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC354" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD354" t="inlineStr">
+        <is>
+          <t>carbon_tax_300_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE354" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\tech_selection\20261007153330_carbon_tax_300_el_price_250</t>
         </is>
       </c>
     </row>
